--- a/tests/bewertung/Bewertung_K1-K10.xlsx
+++ b/tests/bewertung/Bewertung_K1-K10.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Bewertung Nutzwertanalyse – KI-Bildgeneratoren (M306)</t>
   </si>
   <si>
-    <t xml:space="preserve">Stand: 12.10.2026 · Hunger, Weisshaar</t>
+    <t xml:space="preserve">Stand: 25.10.2026 · Hunger, Weisshaar</t>
   </si>
   <si>
     <t xml:space="preserve">So funktioniert die Tabelle</t>
@@ -55,10 +55,10 @@
     <t xml:space="preserve">• Muss-Kriterien K6 und K9: Mit 1 Punkt scheidet ein Tool aus. Bei Gleichstand entscheidet K1.</t>
   </si>
   <si>
-    <t xml:space="preserve">Offene Punkte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Nicolas bewertet in den gelben Zellen: Blatt «K1–K4 pro Prompt» (K1–K4) und Blatt «Nutzwert» (K5–K10).</t>
+    <t xml:space="preserve">Stand der Bewertung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Beide Bewertungen sind abgeschlossen (Nicolas am 25.10.2026). Die Nutzwertanalyse rechnet mit den Mittelwerten.</t>
   </si>
   <si>
     <t xml:space="preserve">• K5–K10 «Lucas» stammen aus dem Word-Dokument (Stand 12.10.2026).</t>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">K1–K4 pro Test-Prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">Ganze Punkte 1–5 (siehe Blatt «Skala»). Leere Zeilen: Test steht noch aus.</t>
+    <t xml:space="preserve">Ganze Punkte 1–5 (siehe Blatt «Skala»).</t>
   </si>
   <si>
     <t xml:space="preserve">Tool</t>
@@ -280,7 +280,7 @@
     <t xml:space="preserve">Rang</t>
   </si>
   <si>
-    <t xml:space="preserve">Hinweis: Nutzwert vorläufig, solange Nicolas noch nicht bewertet hat.</t>
+    <t xml:space="preserve">Nutzwert definitiv: Mittelwerte der Bewertungen von Lucas und Nicolas (25.10.2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Bewertungsskala (aus dem Lastenheft)</t>
@@ -590,107 +590,107 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1154,23 +1154,29 @@
       <c r="C5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E5" s="12" t="n">
         <f aca="false">IF(COUNT(C5:D5)=0,"",AVERAGE(C5:D5))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="H5" s="12" t="n">
         <f aca="false">IF(COUNT(F5:G5)=0,"",AVERAGE(F5:G5))</f>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="11"/>
+      <c r="J5" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K5" s="12" t="n">
         <f aca="false">IF(COUNT(I5:J5)=0,"",AVERAGE(I5:J5))</f>
         <v>5</v>
@@ -1178,7 +1184,9 @@
       <c r="L5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M5" s="11"/>
+      <c r="M5" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N5" s="12" t="n">
         <f aca="false">IF(COUNT(L5:M5)=0,"",AVERAGE(L5:M5))</f>
         <v>5</v>
@@ -1197,15 +1205,19 @@
       <c r="C6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E6" s="12" t="n">
         <f aca="false">IF(COUNT(C6:D6)=0,"",AVERAGE(C6:D6))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="H6" s="12" t="n">
         <f aca="false">IF(COUNT(F6:G6)=0,"",AVERAGE(F6:G6))</f>
         <v>4</v>
@@ -1213,7 +1225,9 @@
       <c r="I6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="11"/>
+      <c r="J6" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K6" s="12" t="n">
         <f aca="false">IF(COUNT(I6:J6)=0,"",AVERAGE(I6:J6))</f>
         <v>5</v>
@@ -1221,7 +1235,9 @@
       <c r="L6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M6" s="11"/>
+      <c r="M6" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N6" s="12" t="n">
         <f aca="false">IF(COUNT(L6:M6)=0,"",AVERAGE(L6:M6))</f>
         <v>5</v>
@@ -1240,15 +1256,19 @@
       <c r="C7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E7" s="12" t="n">
         <f aca="false">IF(COUNT(C7:D7)=0,"",AVERAGE(C7:D7))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="G7" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="H7" s="12" t="n">
         <f aca="false">IF(COUNT(F7:G7)=0,"",AVERAGE(F7:G7))</f>
         <v>4</v>
@@ -1256,7 +1276,9 @@
       <c r="I7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="11"/>
+      <c r="J7" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K7" s="12" t="n">
         <f aca="false">IF(COUNT(I7:J7)=0,"",AVERAGE(I7:J7))</f>
         <v>5</v>
@@ -1264,7 +1286,9 @@
       <c r="L7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M7" s="11"/>
+      <c r="M7" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N7" s="12" t="n">
         <f aca="false">IF(COUNT(L7:M7)=0,"",AVERAGE(L7:M7))</f>
         <v>5</v>
@@ -1283,15 +1307,19 @@
       <c r="C8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E8" s="12" t="n">
         <f aca="false">IF(COUNT(C8:D8)=0,"",AVERAGE(C8:D8))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="11"/>
+      <c r="G8" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="H8" s="12" t="n">
         <f aca="false">IF(COUNT(F8:G8)=0,"",AVERAGE(F8:G8))</f>
         <v>3</v>
@@ -1299,7 +1327,9 @@
       <c r="I8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="11"/>
+      <c r="J8" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K8" s="12" t="n">
         <f aca="false">IF(COUNT(I8:J8)=0,"",AVERAGE(I8:J8))</f>
         <v>5</v>
@@ -1307,10 +1337,12 @@
       <c r="L8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="11"/>
+      <c r="M8" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N8" s="12" t="n">
         <f aca="false">IF(COUNT(L8:M8)=0,"",AVERAGE(L8:M8))</f>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O8" s="13" t="s">
         <v>34</v>
@@ -1326,7 +1358,9 @@
       <c r="C9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E9" s="12" t="n">
         <f aca="false">IF(COUNT(C9:D9)=0,"",AVERAGE(C9:D9))</f>
         <v>4</v>
@@ -1334,23 +1368,29 @@
       <c r="F9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="11"/>
+      <c r="G9" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="H9" s="12" t="n">
         <f aca="false">IF(COUNT(F9:G9)=0,"",AVERAGE(F9:G9))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="11"/>
+      <c r="J9" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="K9" s="12" t="n">
         <f aca="false">IF(COUNT(I9:J9)=0,"",AVERAGE(I9:J9))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M9" s="11"/>
+      <c r="M9" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N9" s="12" t="n">
         <f aca="false">IF(COUNT(L9:M9)=0,"",AVERAGE(L9:M9))</f>
         <v>5</v>
@@ -1369,7 +1409,9 @@
       <c r="C10" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="E10" s="12" t="n">
         <f aca="false">IF(COUNT(C10:D10)=0,"",AVERAGE(C10:D10))</f>
         <v>5</v>
@@ -1377,15 +1419,19 @@
       <c r="F10" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="11"/>
+      <c r="G10" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="H10" s="12" t="n">
         <f aca="false">IF(COUNT(F10:G10)=0,"",AVERAGE(F10:G10))</f>
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="11"/>
+      <c r="J10" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K10" s="12" t="n">
         <f aca="false">IF(COUNT(I10:J10)=0,"",AVERAGE(I10:J10))</f>
         <v>5</v>
@@ -1393,10 +1439,12 @@
       <c r="L10" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M10" s="11"/>
+      <c r="M10" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="N10" s="12" t="n">
         <f aca="false">IF(COUNT(L10:M10)=0,"",AVERAGE(L10:M10))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10" s="13" t="s">
         <v>38</v>
@@ -1412,15 +1460,19 @@
       <c r="C11" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="E11" s="12" t="n">
         <f aca="false">IF(COUNT(C11:D11)=0,"",AVERAGE(C11:D11))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="11"/>
+      <c r="G11" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="H11" s="12" t="n">
         <f aca="false">IF(COUNT(F11:G11)=0,"",AVERAGE(F11:G11))</f>
         <v>5</v>
@@ -1428,7 +1480,9 @@
       <c r="I11" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="11"/>
+      <c r="J11" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K11" s="12" t="n">
         <f aca="false">IF(COUNT(I11:J11)=0,"",AVERAGE(I11:J11))</f>
         <v>5</v>
@@ -1436,7 +1490,9 @@
       <c r="L11" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M11" s="11"/>
+      <c r="M11" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N11" s="12" t="n">
         <f aca="false">IF(COUNT(L11:M11)=0,"",AVERAGE(L11:M11))</f>
         <v>5</v>
@@ -1455,7 +1511,9 @@
       <c r="C12" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="E12" s="12" t="n">
         <f aca="false">IF(COUNT(C12:D12)=0,"",AVERAGE(C12:D12))</f>
         <v>5</v>
@@ -1463,7 +1521,9 @@
       <c r="F12" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="H12" s="12" t="n">
         <f aca="false">IF(COUNT(F12:G12)=0,"",AVERAGE(F12:G12))</f>
         <v>5</v>
@@ -1471,7 +1531,9 @@
       <c r="I12" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="11"/>
+      <c r="J12" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K12" s="12" t="n">
         <f aca="false">IF(COUNT(I12:J12)=0,"",AVERAGE(I12:J12))</f>
         <v>5</v>
@@ -1479,7 +1541,9 @@
       <c r="L12" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M12" s="11"/>
+      <c r="M12" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N12" s="12" t="n">
         <f aca="false">IF(COUNT(L12:M12)=0,"",AVERAGE(L12:M12))</f>
         <v>5</v>
@@ -1498,7 +1562,9 @@
       <c r="C13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="E13" s="12" t="n">
         <f aca="false">IF(COUNT(C13:D13)=0,"",AVERAGE(C13:D13))</f>
         <v>5</v>
@@ -1506,15 +1572,19 @@
       <c r="F13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="H13" s="12" t="n">
         <f aca="false">IF(COUNT(F13:G13)=0,"",AVERAGE(F13:G13))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="11"/>
+      <c r="J13" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K13" s="12" t="n">
         <f aca="false">IF(COUNT(I13:J13)=0,"",AVERAGE(I13:J13))</f>
         <v>5</v>
@@ -1522,7 +1592,9 @@
       <c r="L13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M13" s="11"/>
+      <c r="M13" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N13" s="12" t="n">
         <f aca="false">IF(COUNT(L13:M13)=0,"",AVERAGE(L13:M13))</f>
         <v>5</v>
@@ -1541,15 +1613,19 @@
       <c r="C14" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="11"/>
+      <c r="D14" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E14" s="12" t="n">
         <f aca="false">IF(COUNT(C14:D14)=0,"",AVERAGE(C14:D14))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="11"/>
+      <c r="G14" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="H14" s="12" t="n">
         <f aca="false">IF(COUNT(F14:G14)=0,"",AVERAGE(F14:G14))</f>
         <v>5</v>
@@ -1557,7 +1633,9 @@
       <c r="I14" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="11"/>
+      <c r="J14" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K14" s="12" t="n">
         <f aca="false">IF(COUNT(I14:J14)=0,"",AVERAGE(I14:J14))</f>
         <v>5</v>
@@ -1565,10 +1643,12 @@
       <c r="L14" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="M14" s="11"/>
+      <c r="M14" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N14" s="12" t="n">
         <f aca="false">IF(COUNT(L14:M14)=0,"",AVERAGE(L14:M14))</f>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O14" s="13" t="s">
         <v>43</v>
@@ -1584,7 +1664,9 @@
       <c r="C15" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="E15" s="12" t="n">
         <f aca="false">IF(COUNT(C15:D15)=0,"",AVERAGE(C15:D15))</f>
         <v>5</v>
@@ -1592,15 +1674,19 @@
       <c r="F15" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="H15" s="12" t="n">
         <f aca="false">IF(COUNT(F15:G15)=0,"",AVERAGE(F15:G15))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J15" s="11"/>
+      <c r="J15" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K15" s="12" t="n">
         <f aca="false">IF(COUNT(I15:J15)=0,"",AVERAGE(I15:J15))</f>
         <v>5</v>
@@ -1608,10 +1694,12 @@
       <c r="L15" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M15" s="11"/>
+      <c r="M15" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="N15" s="12" t="n">
         <f aca="false">IF(COUNT(L15:M15)=0,"",AVERAGE(L15:M15))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O15" s="13" t="s">
         <v>44</v>
@@ -1627,15 +1715,19 @@
       <c r="C16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E16" s="12" t="n">
         <f aca="false">IF(COUNT(C16:D16)=0,"",AVERAGE(C16:D16))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="H16" s="12" t="n">
         <f aca="false">IF(COUNT(F16:G16)=0,"",AVERAGE(F16:G16))</f>
         <v>5</v>
@@ -1643,7 +1735,9 @@
       <c r="I16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="11"/>
+      <c r="J16" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K16" s="12" t="n">
         <f aca="false">IF(COUNT(I16:J16)=0,"",AVERAGE(I16:J16))</f>
         <v>5</v>
@@ -1651,7 +1745,9 @@
       <c r="L16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M16" s="11"/>
+      <c r="M16" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N16" s="12" t="n">
         <f aca="false">IF(COUNT(L16:M16)=0,"",AVERAGE(L16:M16))</f>
         <v>5</v>
@@ -1670,15 +1766,19 @@
       <c r="C17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E17" s="12" t="n">
         <f aca="false">IF(COUNT(C17:D17)=0,"",AVERAGE(C17:D17))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="11"/>
+      <c r="G17" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="H17" s="12" t="n">
         <f aca="false">IF(COUNT(F17:G17)=0,"",AVERAGE(F17:G17))</f>
         <v>5</v>
@@ -1686,7 +1786,9 @@
       <c r="I17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J17" s="11"/>
+      <c r="J17" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K17" s="12" t="n">
         <f aca="false">IF(COUNT(I17:J17)=0,"",AVERAGE(I17:J17))</f>
         <v>5</v>
@@ -1694,7 +1796,9 @@
       <c r="L17" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="M17" s="11"/>
+      <c r="M17" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="N17" s="12" t="n">
         <f aca="false">IF(COUNT(L17:M17)=0,"",AVERAGE(L17:M17))</f>
         <v>4</v>
@@ -1713,7 +1817,9 @@
       <c r="C18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="E18" s="12" t="n">
         <f aca="false">IF(COUNT(C18:D18)=0,"",AVERAGE(C18:D18))</f>
         <v>5</v>
@@ -1721,15 +1827,19 @@
       <c r="F18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="11"/>
+      <c r="G18" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="H18" s="12" t="n">
         <f aca="false">IF(COUNT(F18:G18)=0,"",AVERAGE(F18:G18))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J18" s="11"/>
+      <c r="J18" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K18" s="12" t="n">
         <f aca="false">IF(COUNT(I18:J18)=0,"",AVERAGE(I18:J18))</f>
         <v>5</v>
@@ -1737,7 +1847,9 @@
       <c r="L18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M18" s="11"/>
+      <c r="M18" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N18" s="12" t="n">
         <f aca="false">IF(COUNT(L18:M18)=0,"",AVERAGE(L18:M18))</f>
         <v>5</v>
@@ -1756,23 +1868,29 @@
       <c r="C19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E19" s="12" t="n">
         <f aca="false">IF(COUNT(C19:D19)=0,"",AVERAGE(C19:D19))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="11"/>
+      <c r="G19" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="H19" s="12" t="n">
         <f aca="false">IF(COUNT(F19:G19)=0,"",AVERAGE(F19:G19))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J19" s="11"/>
+      <c r="J19" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K19" s="12" t="n">
         <f aca="false">IF(COUNT(I19:J19)=0,"",AVERAGE(I19:J19))</f>
         <v>5</v>
@@ -1780,10 +1898,12 @@
       <c r="L19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M19" s="11"/>
+      <c r="M19" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="N19" s="12" t="n">
         <f aca="false">IF(COUNT(L19:M19)=0,"",AVERAGE(L19:M19))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O19" s="13" t="s">
         <v>49</v>
@@ -1799,15 +1919,19 @@
       <c r="C20" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="E20" s="12" t="n">
         <f aca="false">IF(COUNT(C20:D20)=0,"",AVERAGE(C20:D20))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="H20" s="12" t="n">
         <f aca="false">IF(COUNT(F20:G20)=0,"",AVERAGE(F20:G20))</f>
         <v>5</v>
@@ -1815,7 +1939,9 @@
       <c r="I20" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J20" s="11"/>
+      <c r="J20" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K20" s="12" t="n">
         <f aca="false">IF(COUNT(I20:J20)=0,"",AVERAGE(I20:J20))</f>
         <v>5</v>
@@ -1823,7 +1949,9 @@
       <c r="L20" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M20" s="11"/>
+      <c r="M20" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="N20" s="12" t="n">
         <f aca="false">IF(COUNT(L20:M20)=0,"",AVERAGE(L20:M20))</f>
         <v>5</v>
@@ -1842,7 +1970,9 @@
       <c r="C21" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E21" s="12" t="n">
         <f aca="false">IF(COUNT(C21:D21)=0,"",AVERAGE(C21:D21))</f>
         <v>4</v>
@@ -1850,26 +1980,32 @@
       <c r="F21" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="11"/>
+      <c r="G21" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="H21" s="12" t="n">
         <f aca="false">IF(COUNT(F21:G21)=0,"",AVERAGE(F21:G21))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J21" s="11"/>
+      <c r="J21" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="K21" s="12" t="n">
         <f aca="false">IF(COUNT(I21:J21)=0,"",AVERAGE(I21:J21))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L21" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M21" s="11"/>
+      <c r="M21" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="N21" s="12" t="n">
         <f aca="false">IF(COUNT(L21:M21)=0,"",AVERAGE(L21:M21))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O21" s="13" t="s">
         <v>51</v>
@@ -1885,7 +2021,9 @@
       <c r="C22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="11"/>
+      <c r="D22" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="E22" s="12" t="n">
         <f aca="false">IF(COUNT(C22:D22)=0,"",AVERAGE(C22:D22))</f>
         <v>5</v>
@@ -1893,7 +2031,9 @@
       <c r="F22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="11"/>
+      <c r="G22" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="H22" s="12" t="n">
         <f aca="false">IF(COUNT(F22:G22)=0,"",AVERAGE(F22:G22))</f>
         <v>5</v>
@@ -1901,7 +2041,9 @@
       <c r="I22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J22" s="11"/>
+      <c r="J22" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="K22" s="12" t="n">
         <f aca="false">IF(COUNT(I22:J22)=0,"",AVERAGE(I22:J22))</f>
         <v>5</v>
@@ -1909,10 +2051,12 @@
       <c r="L22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M22" s="11"/>
+      <c r="M22" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="N22" s="12" t="n">
         <f aca="false">IF(COUNT(L22:M22)=0,"",AVERAGE(L22:M22))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O22" s="13" t="s">
         <v>52</v>
@@ -2065,37 +2209,37 @@
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!C5:C10)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!C5:C10),1))</f>
         <v>4.8</v>
       </c>
-      <c r="E5" s="17" t="str">
+      <c r="E5" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!D5:D10)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!D5:D10),1))</f>
-        <v/>
+        <v>4.2</v>
       </c>
       <c r="F5" s="12" t="n">
         <f aca="false">IF(COUNT(D5:E5)=0,"",ROUND(AVERAGE(D5:E5),1))</f>
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="G5" s="16" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!C11:C16)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!C11:C16),1))</f>
         <v>5</v>
       </c>
-      <c r="H5" s="17" t="str">
+      <c r="H5" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!D11:D16)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!D11:D16),1))</f>
-        <v/>
+        <v>4.3</v>
       </c>
       <c r="I5" s="12" t="n">
         <f aca="false">IF(COUNT(G5:H5)=0,"",ROUND(AVERAGE(G5:H5),1))</f>
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J5" s="16" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!C17:C22)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!C17:C22),1))</f>
         <v>4.8</v>
       </c>
-      <c r="K5" s="17" t="str">
+      <c r="K5" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!D17:D22)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!D17:D22),1))</f>
-        <v/>
+        <v>4.2</v>
       </c>
       <c r="L5" s="12" t="n">
         <f aca="false">IF(COUNT(J5:K5)=0,"",ROUND(AVERAGE(J5:K5),1))</f>
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>61</v>
@@ -2115,37 +2259,37 @@
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!F5:F10)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!F5:F10),1))</f>
         <v>4</v>
       </c>
-      <c r="E6" s="17" t="str">
+      <c r="E6" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!G5:G10)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!G5:G10),1))</f>
-        <v/>
+        <v>3.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">IF(COUNT(D6:E6)=0,"",ROUND(AVERAGE(D6:E6),1))</f>
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="G6" s="16" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!F11:F16)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!F11:F16),1))</f>
         <v>5</v>
       </c>
-      <c r="H6" s="17" t="str">
+      <c r="H6" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!G11:G16)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!G11:G16),1))</f>
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="I6" s="12" t="n">
         <f aca="false">IF(COUNT(G6:H6)=0,"",ROUND(AVERAGE(G6:H6),1))</f>
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J6" s="16" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!F17:F22)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!F17:F22),1))</f>
         <v>5</v>
       </c>
-      <c r="K6" s="17" t="str">
+      <c r="K6" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!G17:G22)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!G17:G22),1))</f>
-        <v/>
+        <v>4.2</v>
       </c>
       <c r="L6" s="12" t="n">
         <f aca="false">IF(COUNT(J6:K6)=0,"",ROUND(AVERAGE(J6:K6),1))</f>
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="M6" s="13" t="s">
         <v>63</v>
@@ -2165,21 +2309,21 @@
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!I5:I10)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!I5:I10),1))</f>
         <v>5</v>
       </c>
-      <c r="E7" s="17" t="str">
+      <c r="E7" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!J5:J10)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!J5:J10),1))</f>
-        <v/>
+        <v>4.8</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">IF(COUNT(D7:E7)=0,"",ROUND(AVERAGE(D7:E7),1))</f>
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G7" s="16" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!I11:I16)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!I11:I16),1))</f>
         <v>5</v>
       </c>
-      <c r="H7" s="17" t="str">
+      <c r="H7" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!J11:J16)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!J11:J16),1))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I7" s="12" t="n">
         <f aca="false">IF(COUNT(G7:H7)=0,"",ROUND(AVERAGE(G7:H7),1))</f>
@@ -2189,13 +2333,13 @@
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!I17:I22)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!I17:I22),1))</f>
         <v>5</v>
       </c>
-      <c r="K7" s="17" t="str">
+      <c r="K7" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!J17:J22)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!J17:J22),1))</f>
-        <v/>
+        <v>4.8</v>
       </c>
       <c r="L7" s="12" t="n">
         <f aca="false">IF(COUNT(J7:K7)=0,"",ROUND(AVERAGE(J7:K7),1))</f>
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M7" s="13" t="s">
         <v>65</v>
@@ -2215,9 +2359,9 @@
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!L5:L10)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!L5:L10),1))</f>
         <v>4.8</v>
       </c>
-      <c r="E8" s="17" t="str">
+      <c r="E8" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!M5:M10)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!M5:M10),1))</f>
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">IF(COUNT(D8:E8)=0,"",ROUND(AVERAGE(D8:E8),1))</f>
@@ -2227,9 +2371,9 @@
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!L11:L16)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!L11:L16),1))</f>
         <v>4.8</v>
       </c>
-      <c r="H8" s="17" t="str">
+      <c r="H8" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!M11:M16)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!M11:M16),1))</f>
-        <v/>
+        <v>4.8</v>
       </c>
       <c r="I8" s="12" t="n">
         <f aca="false">IF(COUNT(G8:H8)=0,"",ROUND(AVERAGE(G8:H8),1))</f>
@@ -2239,13 +2383,13 @@
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!L17:L22)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!L17:L22),1))</f>
         <v>4.8</v>
       </c>
-      <c r="K8" s="17" t="str">
+      <c r="K8" s="17" t="n">
         <f aca="false">IF(COUNT('K1–K4 pro Prompt'!M17:M22)=0,"",ROUND(AVERAGE('K1–K4 pro Prompt'!M17:M22),1))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="L8" s="12" t="n">
         <f aca="false">IF(COUNT(J8:K8)=0,"",ROUND(AVERAGE(J8:K8),1))</f>
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>67</v>
@@ -2264,7 +2408,9 @@
       <c r="D9" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="19"/>
+      <c r="E9" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="F9" s="12" t="n">
         <f aca="false">IF(COUNT(D9:E9)=0,"",ROUND(AVERAGE(D9:E9),1))</f>
         <v>5</v>
@@ -2272,7 +2418,9 @@
       <c r="G9" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="19"/>
+      <c r="H9" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="I9" s="12" t="n">
         <f aca="false">IF(COUNT(G9:H9)=0,"",ROUND(AVERAGE(G9:H9),1))</f>
         <v>5</v>
@@ -2280,10 +2428,12 @@
       <c r="J9" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="K9" s="19"/>
+      <c r="K9" s="19" t="n">
+        <v>2</v>
+      </c>
       <c r="L9" s="12" t="n">
         <f aca="false">IF(COUNT(J9:K9)=0,"",ROUND(AVERAGE(J9:K9),1))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" s="13" t="s">
         <v>69</v>
@@ -2302,7 +2452,9 @@
       <c r="D10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="19"/>
+      <c r="E10" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="F10" s="12" t="n">
         <f aca="false">IF(COUNT(D10:E10)=0,"",ROUND(AVERAGE(D10:E10),1))</f>
         <v>5</v>
@@ -2310,7 +2462,9 @@
       <c r="G10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="I10" s="12" t="n">
         <f aca="false">IF(COUNT(G10:H10)=0,"",ROUND(AVERAGE(G10:H10),1))</f>
         <v>5</v>
@@ -2318,7 +2472,9 @@
       <c r="J10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="K10" s="19"/>
+      <c r="K10" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="L10" s="12" t="n">
         <f aca="false">IF(COUNT(J10:K10)=0,"",ROUND(AVERAGE(J10:K10),1))</f>
         <v>5</v>
@@ -2340,15 +2496,19 @@
       <c r="D11" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="19"/>
+      <c r="E11" s="19" t="n">
+        <v>4</v>
+      </c>
       <c r="F11" s="12" t="n">
         <f aca="false">IF(COUNT(D11:E11)=0,"",ROUND(AVERAGE(D11:E11),1))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="19"/>
+      <c r="H11" s="19" t="n">
+        <v>3</v>
+      </c>
       <c r="I11" s="12" t="n">
         <f aca="false">IF(COUNT(G11:H11)=0,"",ROUND(AVERAGE(G11:H11),1))</f>
         <v>3</v>
@@ -2356,7 +2516,9 @@
       <c r="J11" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="19"/>
+      <c r="K11" s="19" t="n">
+        <v>4</v>
+      </c>
       <c r="L11" s="12" t="n">
         <f aca="false">IF(COUNT(J11:K11)=0,"",ROUND(AVERAGE(J11:K11),1))</f>
         <v>4</v>
@@ -2378,7 +2540,9 @@
       <c r="D12" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="19"/>
+      <c r="E12" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="F12" s="12" t="n">
         <f aca="false">IF(COUNT(D12:E12)=0,"",ROUND(AVERAGE(D12:E12),1))</f>
         <v>5</v>
@@ -2386,7 +2550,9 @@
       <c r="G12" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="19"/>
+      <c r="H12" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="I12" s="12" t="n">
         <f aca="false">IF(COUNT(G12:H12)=0,"",ROUND(AVERAGE(G12:H12),1))</f>
         <v>5</v>
@@ -2394,7 +2560,9 @@
       <c r="J12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="19"/>
+      <c r="K12" s="19" t="n">
+        <v>3</v>
+      </c>
       <c r="L12" s="12" t="n">
         <f aca="false">IF(COUNT(J12:K12)=0,"",ROUND(AVERAGE(J12:K12),1))</f>
         <v>3</v>
@@ -2416,7 +2584,9 @@
       <c r="D13" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="19"/>
+      <c r="E13" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="F13" s="12" t="n">
         <f aca="false">IF(COUNT(D13:E13)=0,"",ROUND(AVERAGE(D13:E13),1))</f>
         <v>5</v>
@@ -2424,7 +2594,9 @@
       <c r="G13" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="19"/>
+      <c r="H13" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="I13" s="12" t="n">
         <f aca="false">IF(COUNT(G13:H13)=0,"",ROUND(AVERAGE(G13:H13),1))</f>
         <v>5</v>
@@ -2432,7 +2604,9 @@
       <c r="J13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="19"/>
+      <c r="K13" s="19" t="n">
+        <v>2</v>
+      </c>
       <c r="L13" s="12" t="n">
         <f aca="false">IF(COUNT(J13:K13)=0,"",ROUND(AVERAGE(J13:K13),1))</f>
         <v>2</v>
@@ -2454,7 +2628,9 @@
       <c r="D14" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="F14" s="12" t="n">
         <f aca="false">IF(COUNT(D14:E14)=0,"",ROUND(AVERAGE(D14:E14),1))</f>
         <v>5</v>
@@ -2462,7 +2638,9 @@
       <c r="G14" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="I14" s="12" t="n">
         <f aca="false">IF(COUNT(G14:H14)=0,"",ROUND(AVERAGE(G14:H14),1))</f>
         <v>5</v>
@@ -2470,7 +2648,9 @@
       <c r="J14" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="19"/>
+      <c r="K14" s="19" t="n">
+        <v>4</v>
+      </c>
       <c r="L14" s="12" t="n">
         <f aca="false">IF(COUNT(J14:K14)=0,"",ROUND(AVERAGE(J14:K14),1))</f>
         <v>4</v>
@@ -2512,19 +2692,19 @@
       <c r="E16" s="22"/>
       <c r="F16" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT($B$5:$B$14,F5:F14),2)</f>
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
       <c r="I16" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT($B$5:$B$14,I5:I14),2)</f>
-        <v>4.88</v>
+        <v>4.81</v>
       </c>
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
       <c r="L16" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT($B$5:$B$14,L5:L14),2)</f>
-        <v>4.29</v>
+        <v>4.07</v>
       </c>
       <c r="M16" s="23"/>
     </row>
